--- a/cuisine.xlsx
+++ b/cuisine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/F7829A4895892F0F/astrbot_plugin_petitplanet_cuisine/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leoli\.astrbot\data\plugins\astrbot_plugin_petitplanet_cuisine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="E3FEEAEBBEFEA31ABB059AE62C6B14B1128FF0E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED5C2CDB-4BF0-BA4A-B990-55FCB25B651F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75CA929-8603-4076-AF52-35E5BA6C6D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="278">
   <si>
     <t>分类</t>
   </si>
@@ -224,42 +224,18 @@
     <t>海鲜粥</t>
   </si>
   <si>
-    <t>胡萝卜炖肉(紫)</t>
-  </si>
-  <si>
-    <t>胡萝卜(紫)</t>
-  </si>
-  <si>
     <t>肉</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>四时蔬果汤(紫)</t>
-  </si>
-  <si>
-    <t>[水果类](紫)</t>
-  </si>
-  <si>
     <t>快速翻土一阶</t>
   </si>
   <si>
-    <t>沁凉水果面(紫)</t>
-  </si>
-  <si>
-    <t>小麦(紫)</t>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
-    <t>果香鱼壶(紫)</t>
-  </si>
-  <si>
-    <t>[鱼类](紫)</t>
-  </si>
-  <si>
     <t>70</t>
   </si>
   <si>
@@ -269,9 +245,6 @@
     <t>海鲜大铺面</t>
   </si>
   <si>
-    <t>[海鲜](紫)</t>
-  </si>
-  <si>
     <t>轻盈潜行一阶</t>
   </si>
   <si>
@@ -296,12 +269,6 @@
     <t>水稻</t>
   </si>
   <si>
-    <t>绵密麦奶(紫)</t>
-  </si>
-  <si>
-    <t>[谷物类](紫)</t>
-  </si>
-  <si>
     <t>奶</t>
   </si>
   <si>
@@ -335,9 +302,6 @@
     <t>果酥烤鱼</t>
   </si>
   <si>
-    <t>[海鱼]</t>
-  </si>
-  <si>
     <t>荤菜/烤焙</t>
   </si>
   <si>
@@ -350,9 +314,6 @@
     <t>蔬风烤鱼</t>
   </si>
   <si>
-    <t>海烩焗饭(紫)</t>
-  </si>
-  <si>
     <t>招牌菜</t>
   </si>
   <si>
@@ -377,12 +338,6 @@
     <t>素食/主食</t>
   </si>
   <si>
-    <t>番茄红宋汤(紫)</t>
-  </si>
-  <si>
-    <t>番茄(紫)</t>
-  </si>
-  <si>
     <t>竹笋</t>
   </si>
   <si>
@@ -392,66 +347,21 @@
     <t>素菜/炖菜</t>
   </si>
   <si>
-    <t>茄茄擂辣饭(紫)</t>
-  </si>
-  <si>
-    <t>茄子(紫)</t>
-  </si>
-  <si>
     <t>辣椒</t>
   </si>
   <si>
-    <t>刺锅海胆蒸蛋(紫)</t>
-  </si>
-  <si>
-    <t>海胆(紫)</t>
-  </si>
-  <si>
-    <t>满满大烩菜(紫)</t>
-  </si>
-  <si>
-    <t>玉米(紫)</t>
-  </si>
-  <si>
-    <t>裹裹虾炸鱼(紫)</t>
-  </si>
-  <si>
-    <t>[虾类](紫)</t>
-  </si>
-  <si>
     <t>80</t>
   </si>
   <si>
     <t>荤菜/炸物</t>
   </si>
   <si>
-    <t>鲜笃鱼汤(紫)</t>
-  </si>
-  <si>
-    <t>珍蟹腌笃鲜(紫)</t>
-  </si>
-  <si>
-    <t>[蟹类](紫)</t>
-  </si>
-  <si>
-    <t>辣龙虾过海(紫)</t>
-  </si>
-  <si>
-    <t>龙虾(紫)</t>
-  </si>
-  <si>
     <t>90</t>
   </si>
   <si>
     <t>轻盈潜行二阶</t>
   </si>
   <si>
-    <t>握鱼大手卷(紫)</t>
-  </si>
-  <si>
-    <t>水稻(紫)</t>
-  </si>
-  <si>
     <t>快速翻土二阶</t>
   </si>
   <si>
@@ -461,39 +371,18 @@
     <t>晶彩蒸鱼饭</t>
   </si>
   <si>
-    <t>[淡水鱼](紫)</t>
-  </si>
-  <si>
     <t>钓鱼之力二阶</t>
   </si>
   <si>
-    <t>梦幻锦绣香蔬宴(金)</t>
-  </si>
-  <si>
-    <t>[蔬菜类](金)</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
-    <t>梦幻三仙过海鱼(金)</t>
-  </si>
-  <si>
-    <t>[海鱼](金)</t>
-  </si>
-  <si>
     <t>130</t>
   </si>
   <si>
     <t>钓鱼之力三阶</t>
   </si>
   <si>
-    <t>梦幻双色升鱼宴(紫)</t>
-  </si>
-  <si>
-    <t>[淡水鱼](金)</t>
-  </si>
-  <si>
     <t>[绿色蔬菜]</t>
   </si>
   <si>
@@ -530,18 +419,6 @@
     <t>李子</t>
   </si>
   <si>
-    <t>漫香果麦奶(紫)</t>
-  </si>
-  <si>
-    <t>[水果](紫)</t>
-  </si>
-  <si>
-    <t>珍蔬麦饮(紫)</t>
-  </si>
-  <si>
-    <t>[蔬菜类](紫)</t>
-  </si>
-  <si>
     <t>香米糕</t>
   </si>
   <si>
@@ -551,12 +428,6 @@
     <t>草莓</t>
   </si>
   <si>
-    <t>蒜香流心奶面包(紫)</t>
-  </si>
-  <si>
-    <t>大蒜(紫)</t>
-  </si>
-  <si>
     <t>田园蔬烩披萨</t>
   </si>
   <si>
@@ -566,39 +437,9 @@
     <t>番茄炸鱼披萨</t>
   </si>
   <si>
-    <t>花香蜜瓜派(紫)</t>
-  </si>
-  <si>
-    <t>甜瓜(紫)</t>
-  </si>
-  <si>
-    <t>海岸风情烤串(紫)</t>
-  </si>
-  <si>
-    <t>炙鱼烤虾贝(紫)</t>
-  </si>
-  <si>
-    <t>[海鱼](紫)</t>
-  </si>
-  <si>
-    <t>美味海风披萨(紫)</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
-    <t>水果烤虾拼盘(金)</t>
-  </si>
-  <si>
-    <t>是的，紫色虾</t>
-  </si>
-  <si>
-    <t>梦幻奇迹蒜龙虾(金)</t>
-  </si>
-  <si>
-    <t>龙虾(金)</t>
-  </si>
-  <si>
     <t>大蒜</t>
   </si>
   <si>
@@ -614,21 +455,6 @@
     <t>[蔬菜]</t>
   </si>
   <si>
-    <t>多果流彩捞饭(紫)</t>
-  </si>
-  <si>
-    <t>梦幻仙凤龙虾锅(紫)</t>
-  </si>
-  <si>
-    <t>[龙虾](紫)</t>
-  </si>
-  <si>
-    <t>梦幻金玉满堂饭(金)</t>
-  </si>
-  <si>
-    <t>水稻(金)</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -647,78 +473,33 @@
     <t>160</t>
   </si>
   <si>
-    <t>梦幻海贝海鲜烩(金)</t>
-  </si>
-  <si>
-    <t>[贝类](金)</t>
-  </si>
-  <si>
     <t>170</t>
   </si>
   <si>
-    <t>梦幻海岸虾鱼筵(金)</t>
-  </si>
-  <si>
-    <t>[鱼类](金)</t>
-  </si>
-  <si>
-    <t>梦幻鱼鲜寿司(金)</t>
-  </si>
-  <si>
     <t>180</t>
   </si>
   <si>
-    <t>三色果米糕(紫)</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
     <t>大力撒二阶</t>
   </si>
   <si>
-    <t>时蔬烧烤派对(紫)</t>
-  </si>
-  <si>
-    <t>土豆(紫)</t>
-  </si>
-  <si>
-    <t>黄瓜(紫)</t>
-  </si>
-  <si>
     <t>三色蔬焗饭</t>
   </si>
   <si>
     <t>[黄色蔬菜]</t>
   </si>
   <si>
-    <t>梦幻草莓奶蛋糕(金)</t>
-  </si>
-  <si>
-    <t>草莓(金)</t>
-  </si>
-  <si>
     <t>大力撇三阶</t>
   </si>
   <si>
-    <t>梦幻星莓漫游派(金)</t>
-  </si>
-  <si>
-    <t>蓝莓(金)</t>
-  </si>
-  <si>
     <t>牛奶</t>
   </si>
   <si>
     <t>大力撒三阶</t>
   </si>
   <si>
-    <t>梦幻番茄汤汁面(金)</t>
-  </si>
-  <si>
-    <t>番茄(金)</t>
-  </si>
-  <si>
     <t>家常什锦砂锅</t>
   </si>
   <si>
@@ -731,81 +512,24 @@
     <t>概率出</t>
   </si>
   <si>
-    <t>珍稀什锦砂锅(紫)</t>
-  </si>
-  <si>
-    <t>[素菜]/[荤菜](紫)</t>
-  </si>
-  <si>
-    <t>梦幻什锦砂锅(金)</t>
-  </si>
-  <si>
-    <t>[素菜]/[荤菜](金)</t>
-  </si>
-  <si>
     <t>家常什锦饮</t>
   </si>
   <si>
-    <t>珍稀什锦饮(紫)</t>
-  </si>
-  <si>
-    <t>梦幻什锦饮(金)</t>
-  </si>
-  <si>
     <t>家常什锦烧烤</t>
   </si>
   <si>
     <t>荤素菜/烤焙</t>
   </si>
   <si>
-    <t>珍稀什锦烧烤(紫)</t>
-  </si>
-  <si>
-    <t>梦幻什锦烧烤(金)</t>
-  </si>
-  <si>
-    <t>竹香苹果冰(紫)</t>
-  </si>
-  <si>
-    <t>冬虫夏草煲(紫)</t>
-  </si>
-  <si>
-    <t>[蔬菜](紫)</t>
-  </si>
-  <si>
-    <t>轰炸大菇肉(紫)</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
     <t>荤素菜/炸物</t>
   </si>
   <si>
-    <t>卡拉红汁炖肉(紫)</t>
-  </si>
-  <si>
-    <t>荤菜(紫)</t>
-  </si>
-  <si>
-    <t>独角仙米面包(紫)</t>
-  </si>
-  <si>
-    <t>红穗绛桃包(紫)</t>
-  </si>
-  <si>
-    <t>百果甜甜圈(紫)</t>
-  </si>
-  <si>
-    <t>方便露营烤鱼(紫)</t>
-  </si>
-  <si>
     <t>烤焙</t>
   </si>
   <si>
-    <t>云朵小饼干(紫)</t>
-  </si>
-  <si>
     <t>？</t>
   </si>
   <si>
@@ -843,15 +567,6 @@
   </si>
   <si>
     <t>通过鹤玉获得食谱</t>
-  </si>
-  <si>
-    <t>更新日期：2026.9.29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通过哈佩诺获得食谱
-荤菜就是紫虾紫螃蟹什么的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>版本</t>
@@ -870,10 +585,295 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>茄子[紫]</t>
-  </si>
-  <si>
     <t>素菜/？</t>
+  </si>
+  <si>
+    <t>是的，*紫*色虾</t>
+  </si>
+  <si>
+    <t>通过哈佩诺获得食谱
+荤菜就是*紫*虾*紫*螃蟹什么的</t>
+  </si>
+  <si>
+    <t>茄子[*紫*]</t>
+  </si>
+  <si>
+    <t>梦幻锦绣香蔬宴(*金*)</t>
+  </si>
+  <si>
+    <t>[蔬菜类](*金*)</t>
+  </si>
+  <si>
+    <t>梦幻三仙过海鱼(*金*)</t>
+  </si>
+  <si>
+    <t>[海鱼](*金*)</t>
+  </si>
+  <si>
+    <t>[淡水鱼](*金*)</t>
+  </si>
+  <si>
+    <t>水果烤虾拼盘(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻奇迹蒜龙虾(*金*)</t>
+  </si>
+  <si>
+    <t>龙虾(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻*金*玉满堂饭(*金*)</t>
+  </si>
+  <si>
+    <t>水稻(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻海贝海鲜烩(*金*)</t>
+  </si>
+  <si>
+    <t>[贝类](*金*)</t>
+  </si>
+  <si>
+    <t>梦幻海岸虾鱼筵(*金*)</t>
+  </si>
+  <si>
+    <t>[鱼类](*金*)</t>
+  </si>
+  <si>
+    <t>梦幻鱼鲜寿司(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻草莓奶蛋糕(*金*)</t>
+  </si>
+  <si>
+    <t>草莓(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻星莓漫游派(*金*)</t>
+  </si>
+  <si>
+    <t>蓝莓(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻番茄汤汁面(*金*)</t>
+  </si>
+  <si>
+    <t>番茄(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻什锦砂锅(*金*)</t>
+  </si>
+  <si>
+    <t>[素菜]/[荤菜](*金*)</t>
+  </si>
+  <si>
+    <t>梦幻什锦饮(*金*)</t>
+  </si>
+  <si>
+    <t>梦幻什锦烧烤(*金*)</t>
+  </si>
+  <si>
+    <t>胡萝卜炖肉(紫)</t>
+  </si>
+  <si>
+    <t>胡萝卜(紫)</t>
+  </si>
+  <si>
+    <t>四时蔬果汤(紫)</t>
+  </si>
+  <si>
+    <t>[水果类](紫)</t>
+  </si>
+  <si>
+    <t>沁凉水果面(紫)</t>
+  </si>
+  <si>
+    <t>小麦(紫)</t>
+  </si>
+  <si>
+    <t>果香鱼壶(紫)</t>
+  </si>
+  <si>
+    <t>[鱼类](紫)</t>
+  </si>
+  <si>
+    <t>[海鲜](紫)</t>
+  </si>
+  <si>
+    <t>绵密麦奶(紫)</t>
+  </si>
+  <si>
+    <t>[谷物类](紫)</t>
+  </si>
+  <si>
+    <t>海烩焗饭(紫)</t>
+  </si>
+  <si>
+    <t>番茄红宋汤(紫)</t>
+  </si>
+  <si>
+    <t>番茄(紫)</t>
+  </si>
+  <si>
+    <t>茄茄擂辣饭(紫)</t>
+  </si>
+  <si>
+    <t>茄子(紫)</t>
+  </si>
+  <si>
+    <t>刺锅海胆蒸蛋(紫)</t>
+  </si>
+  <si>
+    <t>海胆(紫)</t>
+  </si>
+  <si>
+    <t>满满大烩菜(紫)</t>
+  </si>
+  <si>
+    <t>玉米(紫)</t>
+  </si>
+  <si>
+    <t>裹裹虾炸鱼(紫)</t>
+  </si>
+  <si>
+    <t>[虾类](紫)</t>
+  </si>
+  <si>
+    <t>鲜笃鱼汤(紫)</t>
+  </si>
+  <si>
+    <t>珍蟹腌笃鲜(紫)</t>
+  </si>
+  <si>
+    <t>[蟹类](紫)</t>
+  </si>
+  <si>
+    <t>辣龙虾过海(紫)</t>
+  </si>
+  <si>
+    <t>龙虾(紫)</t>
+  </si>
+  <si>
+    <t>握鱼大手卷(紫)</t>
+  </si>
+  <si>
+    <t>水稻(紫)</t>
+  </si>
+  <si>
+    <t>[淡水鱼](紫)</t>
+  </si>
+  <si>
+    <t>梦幻双色升鱼宴(紫)</t>
+  </si>
+  <si>
+    <t>漫香果麦奶(紫)</t>
+  </si>
+  <si>
+    <t>[水果](紫)</t>
+  </si>
+  <si>
+    <t>珍蔬麦饮(紫)</t>
+  </si>
+  <si>
+    <t>[蔬菜类](紫)</t>
+  </si>
+  <si>
+    <t>蒜香流心奶面包(紫)</t>
+  </si>
+  <si>
+    <t>大蒜(紫)</t>
+  </si>
+  <si>
+    <t>花香蜜瓜派(紫)</t>
+  </si>
+  <si>
+    <t>甜瓜(紫)</t>
+  </si>
+  <si>
+    <t>海岸风情烤串(紫)</t>
+  </si>
+  <si>
+    <t>炙鱼烤虾贝(紫)</t>
+  </si>
+  <si>
+    <t>[海鱼](紫)</t>
+  </si>
+  <si>
+    <t>美味海风披萨(紫)</t>
+  </si>
+  <si>
+    <t>多果流彩捞饭(紫)</t>
+  </si>
+  <si>
+    <t>梦幻仙凤龙虾锅(紫)</t>
+  </si>
+  <si>
+    <t>[龙虾](紫)</t>
+  </si>
+  <si>
+    <t>三色果米糕(紫)</t>
+  </si>
+  <si>
+    <t>时蔬烧烤派对(紫)</t>
+  </si>
+  <si>
+    <t>土豆(紫)</t>
+  </si>
+  <si>
+    <t>黄瓜(紫)</t>
+  </si>
+  <si>
+    <t>珍稀什锦砂锅(紫)</t>
+  </si>
+  <si>
+    <t>[素菜]/[荤菜](紫)</t>
+  </si>
+  <si>
+    <t>珍稀什锦饮(紫)</t>
+  </si>
+  <si>
+    <t>珍稀什锦烧烤(紫)</t>
+  </si>
+  <si>
+    <t>竹香苹果冰(紫)</t>
+  </si>
+  <si>
+    <t>冬虫夏草煲(紫)</t>
+  </si>
+  <si>
+    <t>[蔬菜](紫)</t>
+  </si>
+  <si>
+    <t>轰炸大菇肉(紫)</t>
+  </si>
+  <si>
+    <t>卡拉红汁炖肉(紫)</t>
+  </si>
+  <si>
+    <t>荤菜(紫)</t>
+  </si>
+  <si>
+    <t>独角仙米面包(紫)</t>
+  </si>
+  <si>
+    <t>红穗绛桃包(紫)</t>
+  </si>
+  <si>
+    <t>百果甜甜圈(紫)</t>
+  </si>
+  <si>
+    <t>方便露营烤鱼(紫)</t>
+  </si>
+  <si>
+    <t>云朵小饼干(紫)</t>
+  </si>
+  <si>
+    <t>更新日期：2026.9.29111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[海鱼]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1261,18 +1261,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N105"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="26.125" customWidth="1"/>
+    <col min="11" max="11" width="26.08203125" customWidth="1"/>
     <col min="12" max="12" width="8.75" customWidth="1"/>
-    <col min="13" max="13" width="23.875" customWidth="1"/>
+    <col min="13" max="13" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1307,16 +1307,16 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>272</v>
+        <v>178</v>
       </c>
       <c r="M1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -2108,18 +2108,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -2131,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I20" t="s">
         <v>59</v>
@@ -2152,18 +2152,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2175,13 +2175,13 @@
         <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I21" t="s">
         <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K21" t="s">
         <v>11</v>
@@ -2196,18 +2196,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2219,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
         <v>39</v>
@@ -2240,18 +2240,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -2263,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s">
         <v>59</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K23" t="s">
         <v>11</v>
@@ -2284,18 +2284,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -2307,13 +2307,13 @@
         <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s">
         <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K24" t="s">
         <v>11</v>
@@ -2328,12 +2328,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -2348,7 +2348,7 @@
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -2372,12 +2372,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>20</v>
@@ -2392,10 +2392,10 @@
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
@@ -2416,12 +2416,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
         <v>41</v>
@@ -2436,10 +2436,10 @@
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
@@ -2460,15 +2460,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -2480,10 +2480,10 @@
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
@@ -2504,18 +2504,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -2524,16 +2524,16 @@
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K29" t="s">
         <v>11</v>
@@ -2548,12 +2548,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>20</v>
@@ -2568,13 +2568,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s">
         <v>11</v>
@@ -2592,18 +2592,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -2612,13 +2612,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s">
         <v>83</v>
-      </c>
-      <c r="I31" t="s">
-        <v>94</v>
       </c>
       <c r="J31" t="s">
         <v>45</v>
@@ -2636,18 +2636,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
@@ -2656,14 +2656,14 @@
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s">
         <v>83</v>
       </c>
-      <c r="I32" t="s">
-        <v>94</v>
-      </c>
       <c r="J32" t="s">
         <v>11</v>
       </c>
@@ -2680,12 +2680,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
         <v>41</v>
@@ -2700,13 +2700,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
         <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J33" t="s">
         <v>11</v>
@@ -2724,12 +2724,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
@@ -2744,7 +2744,7 @@
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s">
         <v>53</v>
@@ -2768,18 +2768,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>277</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
@@ -2788,13 +2788,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s">
         <v>53</v>
       </c>
       <c r="I35" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s">
         <v>11</v>
@@ -2812,18 +2812,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
@@ -2832,16 +2832,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
         <v>53</v>
       </c>
       <c r="I36" t="s">
-        <v>101</v>
-      </c>
-      <c r="J36" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s">
         <v>11</v>
@@ -2856,12 +2853,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
         <v>41</v>
@@ -2876,13 +2873,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s">
         <v>53</v>
       </c>
       <c r="I37" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J37" t="s">
         <v>11</v>
@@ -2900,15 +2897,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="D38" t="s">
         <v>43</v>
@@ -2920,16 +2917,16 @@
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I38" t="s">
         <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K38" t="s">
         <v>11</v>
@@ -2944,21 +2941,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -2988,21 +2985,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -3011,10 +3008,10 @@
         <v>16</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="J40" t="s">
         <v>11</v>
@@ -3032,21 +3029,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -3055,13 +3052,13 @@
         <v>16</v>
       </c>
       <c r="H41" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I41" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K41" t="s">
         <v>11</v>
@@ -3076,21 +3073,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -3099,7 +3096,7 @@
         <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I42" t="s">
         <v>39</v>
@@ -3120,21 +3117,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>227</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="D43" t="s">
         <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
@@ -3143,13 +3140,13 @@
         <v>16</v>
       </c>
       <c r="H43" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I43" t="s">
         <v>54</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K43" t="s">
         <v>11</v>
@@ -3164,18 +3161,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>229</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="E44" t="s">
         <v>41</v>
@@ -3187,13 +3184,13 @@
         <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I44" t="s">
         <v>47</v>
       </c>
       <c r="J44" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K44" t="s">
         <v>11</v>
@@ -3208,12 +3205,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
@@ -3222,7 +3219,7 @@
         <v>43</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -3231,13 +3228,13 @@
         <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I45" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K45" t="s">
         <v>11</v>
@@ -3252,21 +3249,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -3275,13 +3272,13 @@
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I46" t="s">
         <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K46" t="s">
         <v>11</v>
@@ -3296,21 +3293,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E47" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -3319,7 +3316,7 @@
         <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I47" t="s">
         <v>23</v>
@@ -3340,21 +3337,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="C48" t="s">
         <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -3363,13 +3360,13 @@
         <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I48" t="s">
         <v>59</v>
       </c>
       <c r="J48" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K48" t="s">
         <v>11</v>
@@ -3384,12 +3381,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
@@ -3398,7 +3395,7 @@
         <v>41</v>
       </c>
       <c r="E49" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -3407,13 +3404,13 @@
         <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I49" t="s">
         <v>61</v>
       </c>
       <c r="J49" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K49" t="s">
         <v>11</v>
@@ -3428,12 +3425,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
         <v>25</v>
@@ -3442,7 +3439,7 @@
         <v>41</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
@@ -3451,13 +3448,13 @@
         <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I50" t="s">
         <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K50" t="s">
         <v>11</v>
@@ -3472,18 +3469,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E51" t="s">
         <v>41</v>
@@ -3495,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I51" t="s">
         <v>61</v>
       </c>
       <c r="J51" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="K51" t="s">
         <v>11</v>
@@ -3516,21 +3513,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
@@ -3539,13 +3536,13 @@
         <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="I52" t="s">
         <v>47</v>
       </c>
       <c r="J52" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K52" t="s">
         <v>11</v>
@@ -3560,15 +3557,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
         <v>22</v>
@@ -3583,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I53" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="J53" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="K53" t="s">
         <v>11</v>
@@ -3604,21 +3601,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C54" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
@@ -3627,13 +3624,13 @@
         <v>16</v>
       </c>
       <c r="H54" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="I54" t="s">
         <v>59</v>
       </c>
       <c r="J54" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="K54" t="s">
         <v>11</v>
@@ -3648,27 +3645,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H55" t="s">
         <v>26</v>
@@ -3692,27 +3689,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
         <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H56" t="s">
         <v>53</v>
@@ -3736,30 +3733,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E57" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H57" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
@@ -3780,30 +3777,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="E58" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
@@ -3824,30 +3821,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="C59" t="s">
         <v>38</v>
       </c>
       <c r="D59" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I59" t="s">
         <v>18</v>
@@ -3868,12 +3865,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
         <v>38</v>
@@ -3882,16 +3879,16 @@
         <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H60" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I60" t="s">
         <v>18</v>
@@ -3912,33 +3909,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
         <v>43</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J61" t="s">
         <v>11</v>
@@ -3956,18 +3953,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E62" t="s">
         <v>38</v>
@@ -3976,13 +3973,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J62" t="s">
         <v>11</v>
@@ -4000,18 +3997,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="C63" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E63" t="s">
         <v>38</v>
@@ -4020,16 +4017,16 @@
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J63" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K63" t="s">
         <v>11</v>
@@ -4044,12 +4041,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
@@ -4058,22 +4055,22 @@
         <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I64" t="s">
         <v>39</v>
       </c>
       <c r="J64" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K64" t="s">
         <v>11</v>
@@ -4088,12 +4085,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
@@ -4108,16 +4105,16 @@
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I65" t="s">
         <v>61</v>
       </c>
       <c r="J65" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -4132,18 +4129,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B66" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="E66" t="s">
         <v>38</v>
@@ -4152,13 +4149,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J66" t="s">
         <v>48</v>
@@ -4176,36 +4173,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J67" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K67" t="s">
         <v>11</v>
@@ -4220,15 +4217,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="C68" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="D68" t="s">
         <v>30</v>
@@ -4240,16 +4237,16 @@
         <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I68" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J68" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K68" t="s">
         <v>11</v>
@@ -4264,12 +4261,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="C69" t="s">
         <v>29</v>
@@ -4278,22 +4275,22 @@
         <v>41</v>
       </c>
       <c r="E69" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I69" t="s">
         <v>61</v>
       </c>
       <c r="J69" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K69" t="s">
         <v>11</v>
@@ -4308,15 +4305,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="D70" t="s">
         <v>29</v>
@@ -4328,19 +4325,19 @@
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="I70" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J70" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K70" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L70">
         <v>0.95</v>
@@ -4352,18 +4349,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D71" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="E71" t="s">
         <v>41</v>
@@ -4372,16 +4369,16 @@
         <v>57</v>
       </c>
       <c r="G71" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="I71" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J71" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="K71" t="s">
         <v>11</v>
@@ -4396,30 +4393,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
         <v>38</v>
       </c>
       <c r="D72" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
         <v>22</v>
       </c>
       <c r="F72" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
       </c>
       <c r="H72" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I72" t="s">
         <v>39</v>
@@ -4440,30 +4437,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D73" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E73" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F73" t="s">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I73" t="s">
         <v>39</v>
@@ -4484,15 +4481,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B74" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="C74" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s">
         <v>52</v>
@@ -4507,13 +4504,13 @@
         <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="I74" t="s">
         <v>59</v>
       </c>
       <c r="J74" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="K74" t="s">
         <v>11</v>
@@ -4528,21 +4525,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E75" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F75" t="s">
         <v>41</v>
@@ -4551,13 +4548,13 @@
         <v>16</v>
       </c>
       <c r="H75" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="I75" t="s">
         <v>39</v>
       </c>
       <c r="J75" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="K75" t="s">
         <v>11</v>
@@ -4572,36 +4569,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
         <v>50</v>
       </c>
       <c r="E76" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="I76" t="s">
         <v>39</v>
       </c>
       <c r="J76" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="K76" t="s">
         <v>11</v>
@@ -4616,15 +4613,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D77" t="s">
         <v>22</v>
@@ -4639,13 +4636,13 @@
         <v>16</v>
       </c>
       <c r="H77" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="I77" t="s">
         <v>59</v>
       </c>
       <c r="J77" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="K77" t="s">
         <v>11</v>
@@ -4660,15 +4657,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D78" t="s">
         <v>41</v>
@@ -4683,13 +4680,13 @@
         <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="I78" t="s">
         <v>54</v>
       </c>
       <c r="J78" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="K78" t="s">
         <v>11</v>
@@ -4704,21 +4701,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F79" t="s">
         <v>41</v>
@@ -4727,145 +4724,145 @@
         <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="I79" t="s">
         <v>61</v>
       </c>
       <c r="J79" t="s">
+        <v>115</v>
+      </c>
+      <c r="K79" t="s">
+        <v>11</v>
+      </c>
+      <c r="L79">
+        <v>0.95</v>
+      </c>
+      <c r="M79" t="s">
+        <v>11</v>
+      </c>
+      <c r="N79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>137</v>
+      </c>
+      <c r="B80" t="s">
+        <v>257</v>
+      </c>
+      <c r="C80" t="s">
+        <v>239</v>
+      </c>
+      <c r="D80" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" t="s">
+        <v>97</v>
+      </c>
+      <c r="G80" t="s">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s">
+        <v>148</v>
+      </c>
+      <c r="I80" t="s">
+        <v>83</v>
+      </c>
+      <c r="J80" t="s">
+        <v>149</v>
+      </c>
+      <c r="K80" t="s">
+        <v>11</v>
+      </c>
+      <c r="L80">
+        <v>0.95</v>
+      </c>
+      <c r="M80" t="s">
+        <v>11</v>
+      </c>
+      <c r="N80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>137</v>
+      </c>
+      <c r="B81" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" t="s">
+        <v>224</v>
+      </c>
+      <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" t="s">
+        <v>259</v>
+      </c>
+      <c r="F81" t="s">
+        <v>260</v>
+      </c>
+      <c r="G81" t="s">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s">
+        <v>148</v>
+      </c>
+      <c r="I81" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s">
+        <v>109</v>
+      </c>
+      <c r="K81" t="s">
+        <v>11</v>
+      </c>
+      <c r="L81">
+        <v>0.95</v>
+      </c>
+      <c r="M81" t="s">
+        <v>11</v>
+      </c>
+      <c r="N81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>137</v>
+      </c>
+      <c r="B82" t="s">
         <v>150</v>
       </c>
-      <c r="K79" t="s">
-        <v>11</v>
-      </c>
-      <c r="L79">
-        <v>0.95</v>
-      </c>
-      <c r="M79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.1">
-      <c r="A80" t="s">
-        <v>190</v>
-      </c>
-      <c r="B80" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s">
-        <v>138</v>
-      </c>
-      <c r="D80" t="s">
-        <v>112</v>
-      </c>
-      <c r="E80" t="s">
-        <v>111</v>
-      </c>
-      <c r="F80" t="s">
-        <v>110</v>
-      </c>
-      <c r="G80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H80" t="s">
-        <v>212</v>
-      </c>
-      <c r="I80" t="s">
-        <v>94</v>
-      </c>
-      <c r="J80" t="s">
-        <v>213</v>
-      </c>
-      <c r="K80" t="s">
-        <v>11</v>
-      </c>
-      <c r="L80">
-        <v>0.95</v>
-      </c>
-      <c r="M80" t="s">
-        <v>11</v>
-      </c>
-      <c r="N80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.1">
-      <c r="A81" t="s">
-        <v>190</v>
-      </c>
-      <c r="B81" t="s">
-        <v>214</v>
-      </c>
-      <c r="C81" t="s">
-        <v>115</v>
-      </c>
-      <c r="D81" t="s">
-        <v>64</v>
-      </c>
-      <c r="E81" t="s">
-        <v>215</v>
-      </c>
-      <c r="F81" t="s">
-        <v>216</v>
-      </c>
-      <c r="G81" t="s">
-        <v>91</v>
-      </c>
-      <c r="H81" t="s">
-        <v>212</v>
-      </c>
-      <c r="I81" t="s">
-        <v>92</v>
-      </c>
-      <c r="J81" t="s">
-        <v>139</v>
-      </c>
-      <c r="K81" t="s">
-        <v>11</v>
-      </c>
-      <c r="L81">
-        <v>0.95</v>
-      </c>
-      <c r="M81" t="s">
-        <v>11</v>
-      </c>
-      <c r="N81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.1">
-      <c r="A82" t="s">
-        <v>190</v>
-      </c>
-      <c r="B82" t="s">
-        <v>217</v>
-      </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="E82" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="F82" t="s">
-        <v>218</v>
+        <v>151</v>
       </c>
       <c r="G82" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I82" t="s">
         <v>39</v>
       </c>
       <c r="J82" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="K82" t="s">
         <v>11</v>
@@ -4880,36 +4877,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B83" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C83" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D83" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E83" t="s">
         <v>38</v>
       </c>
       <c r="F83" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J83" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="K83" t="s">
         <v>11</v>
@@ -4924,18 +4921,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B84" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="C84" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D84" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
@@ -4944,60 +4941,60 @@
         <v>57</v>
       </c>
       <c r="G84" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s">
+        <v>146</v>
+      </c>
+      <c r="I84" t="s">
+        <v>83</v>
+      </c>
+      <c r="J84" t="s">
+        <v>154</v>
+      </c>
+      <c r="K84" t="s">
+        <v>11</v>
+      </c>
+      <c r="L84">
+        <v>0.95</v>
+      </c>
+      <c r="M84" t="s">
+        <v>11</v>
+      </c>
+      <c r="N84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>137</v>
+      </c>
+      <c r="B85" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" t="s">
         <v>206</v>
-      </c>
-      <c r="I84" t="s">
-        <v>94</v>
-      </c>
-      <c r="J84" t="s">
-        <v>225</v>
-      </c>
-      <c r="K84" t="s">
-        <v>11</v>
-      </c>
-      <c r="L84">
-        <v>0.95</v>
-      </c>
-      <c r="M84" t="s">
-        <v>11</v>
-      </c>
-      <c r="N84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.1">
-      <c r="A85" t="s">
-        <v>190</v>
-      </c>
-      <c r="B85" t="s">
-        <v>226</v>
-      </c>
-      <c r="C85" t="s">
-        <v>227</v>
       </c>
       <c r="D85" t="s">
         <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="F85" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G85" t="s">
         <v>16</v>
       </c>
       <c r="H85" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="I85" t="s">
         <v>39</v>
       </c>
       <c r="J85" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="K85" t="s">
         <v>11</v>
@@ -5012,18 +5009,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="D86" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
@@ -5038,10 +5035,10 @@
         <v>53</v>
       </c>
       <c r="I86" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="J86" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K86" t="s">
         <v>11</v>
@@ -5056,18 +5053,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="C87" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
@@ -5079,13 +5076,13 @@
         <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I87" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="J87" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K87" t="s">
         <v>11</v>
@@ -5100,18 +5097,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="C88" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D88" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -5123,13 +5120,13 @@
         <v>16</v>
       </c>
       <c r="H88" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I88" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="J88" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K88" t="s">
         <v>11</v>
@@ -5144,18 +5141,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
@@ -5164,7 +5161,7 @@
         <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H89" t="s">
         <v>26</v>
@@ -5173,7 +5170,7 @@
         <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K89" t="s">
         <v>11</v>
@@ -5188,18 +5185,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C90" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="D90" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
@@ -5208,16 +5205,16 @@
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
       </c>
       <c r="J90" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K90" t="s">
         <v>11</v>
@@ -5232,18 +5229,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B91" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="C91" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D91" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
@@ -5252,16 +5249,16 @@
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H91" t="s">
-        <v>212</v>
+        <v>148</v>
       </c>
       <c r="I91" t="s">
         <v>18</v>
       </c>
       <c r="J91" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K91" t="s">
         <v>11</v>
@@ -5276,18 +5273,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="C92" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="D92" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
@@ -5296,16 +5293,16 @@
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s">
         <v>53</v>
       </c>
       <c r="I92" t="s">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="J92" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K92" t="s">
         <v>11</v>
@@ -5320,18 +5317,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C93" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
@@ -5340,16 +5337,16 @@
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I93" t="s">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="J93" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K93" t="s">
         <v>11</v>
@@ -5364,18 +5361,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="C94" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
@@ -5384,16 +5381,16 @@
         <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I94" t="s">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="J94" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="K94" t="s">
         <v>11</v>
@@ -5408,18 +5405,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C95" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D95" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
@@ -5431,16 +5428,16 @@
         <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J95" t="s">
         <v>45</v>
       </c>
       <c r="K95" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="L95">
         <v>0.95</v>
@@ -5452,21 +5449,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C96" t="s">
         <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E96" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
@@ -5475,7 +5472,7 @@
         <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I96" t="s">
         <v>11</v>
@@ -5484,7 +5481,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="L96">
         <v>0.95</v>
@@ -5496,21 +5493,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C97" t="s">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="D97" t="s">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="E97" t="s">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -5519,16 +5516,16 @@
         <v>16</v>
       </c>
       <c r="H97" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I97" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="J97" t="s">
         <v>11</v>
       </c>
       <c r="K97" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="L97">
         <v>0.95</v>
@@ -5540,15 +5537,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="98" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C98" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D98" t="s">
         <v>43</v>
@@ -5563,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="H98" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I98" t="s">
         <v>11</v>
@@ -5572,27 +5569,27 @@
         <v>11</v>
       </c>
       <c r="K98" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L98">
+        <v>0.95</v>
+      </c>
+      <c r="M98" t="s">
+        <v>11</v>
+      </c>
+      <c r="N98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>166</v>
+      </c>
+      <c r="B99" t="s">
         <v>271</v>
       </c>
-      <c r="L98">
-        <v>0.95</v>
-      </c>
-      <c r="M98" t="s">
-        <v>11</v>
-      </c>
-      <c r="N98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.1">
-      <c r="A99" t="s">
-        <v>258</v>
-      </c>
-      <c r="B99" t="s">
-        <v>251</v>
-      </c>
       <c r="C99" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="D99" t="s">
         <v>20</v>
@@ -5604,19 +5601,19 @@
         <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J99" t="s">
         <v>45</v>
       </c>
       <c r="K99" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="L99">
         <v>0.95</v>
@@ -5628,18 +5625,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C100" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="D100" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
@@ -5648,19 +5645,19 @@
         <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J100" t="s">
         <v>48</v>
       </c>
       <c r="K100" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="L100">
         <v>0.95</v>
@@ -5672,18 +5669,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C101" t="s">
         <v>38</v>
       </c>
       <c r="D101" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="E101" t="s">
         <v>11</v>
@@ -5692,19 +5689,19 @@
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J101" t="s">
         <v>11</v>
       </c>
       <c r="K101" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="L101">
         <v>0.95</v>
@@ -5716,15 +5713,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B102" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C102" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="D102" t="s">
         <v>25</v>
@@ -5736,19 +5733,19 @@
         <v>11</v>
       </c>
       <c r="G102" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="I102" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
         <v>11</v>
       </c>
       <c r="K102" t="s">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="L102">
         <v>0.95</v>
@@ -5760,15 +5757,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B103" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -5780,7 +5777,7 @@
         <v>11</v>
       </c>
       <c r="G103" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s">
         <v>11</v>
@@ -5789,10 +5786,10 @@
         <v>11</v>
       </c>
       <c r="J103" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="K103" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="L103">
         <v>0.95</v>
@@ -5804,21 +5801,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B104" t="s">
-        <v>274</v>
+        <v>180</v>
       </c>
       <c r="C104" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="D104" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E104" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -5830,13 +5827,13 @@
         <v>11</v>
       </c>
       <c r="I104" t="s">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="J104" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="K104" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="L104">
         <v>0.95</v>
@@ -5848,12 +5845,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.1">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="B105" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
         <v>38</v>
@@ -5862,13 +5859,13 @@
         <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H105">
         <v>35</v>
       </c>
       <c r="K105" t="s">
-        <v>273</v>
+        <v>179</v>
       </c>
       <c r="L105">
         <v>0.95</v>
@@ -5879,7 +5876,7 @@
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A6:K85 B1:K1 A87:K94 B86:K86 A104 B95:J95 M95:N95 A96:J96 M96:N96 A97:J97 M97:N97 A98:J98 M98:N98 A99:C99 M99:N99 A100:J100 M100:N100 A101:J101 M101:N101 A102:J102 M102:N102 A103:I103 M103:N103 M104:N104 F104 E99:J99 N1 A2:K2 M2:N2 A3:K5 M3:N5 M6:N85 M87:N94 M86:N86 H104" numberStoredAsText="1"/>
+    <ignoredError sqref="A6:K19 B1:K1 A89:K89 B86:K86 A104 C95 M95:N95 A96 M96:N96 A97 M97:N97 A98 M98:N98 A99 M99:N99 A100 M100:N100 A101 M101:N101 A102 M102:N102 A103 M103:N103 M104:N104 F104 E99:J99 N1 A2:K2 M2:N2 A3:K5 M3:N5 M6:N85 M87:N94 M86:N86 H104 A25:K28 A20 D20:K20 A21 C21 E21:K21 A22 C22 E22:K22 A23 C23 E23:K23 A24:C24 E24:K24 A30:K34 A29 D29:K29 A39:K40 A38 D38:K38 A53 A41 D41:K41 A42 D42:K42 A43 D43:K43 A44 C44 E44:K44 A45 C45:D45 F45:K45 A46 C46:D46 F46:K46 A47 C47:D47 F47:K47 A48 C48:D48 F48:K48 A49 C49:D49 F49:K49 A50:D50 F50:K50 A51:B51 D51:K51 A55:K58 A54 D54:K54 A61:K62 A59 C59:D59 F59:K59 A60 C60:D60 F60:K60 A64:K65 A63 D63:K63 A72:K72 A66 C66 E66:K66 A67 D67:K67 A68 D68:K68 A69 C69:D69 F69:K69 A70 D70:J70 A79 A73 C73:E73 G73:K73 A74 D74:K74 A85 A80 D80:K80 A81 G81:K81 A82:B82 D82:K82 A87 D87:K87 A92:K92 A90 C90:K90 A94 A93 D93:K93 E95:J95 C96:D96 F96:J96 C97:J97 D98:J98 D100:J100 C101 E101:J101 D102:J102 C103:I103 A37:K37 A36:I36 K36 A52 C52:D52 F52:K52 D53:K53 A71 D71:K71 A75 D75:K75 A76:B76 D76:K76 A77 D77:K77 A78 D78:K78 D79:K79 A83 D83:K83 A84 D84:K84 D85:K85 A88 D88:K88 A91 D91:K91 D94:K94 A35:C35 E35:K35" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>